--- a/r4-core-131-Gemeindecode/StructureDefinition-at-core-organization.xlsx
+++ b/r4-core-131-Gemeindecode/StructureDefinition-at-core-organization.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-organization</t>
+    <t>https://fhir.hl7.at/core/r4/StructureDefinition/at-core-organization</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-07T12:03:29+00:00</t>
+    <t>2026-09-11T12:27:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -361,7 +361,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -609,7 +609,7 @@
     <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -718,7 +718,7 @@
     <t>Organization.identifier.assigner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -796,7 +796,7 @@
     <t>Aa resource (or, for logical models, the URI of the logical model).</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/resource-types</t>
+    <t>http://hl7.org/fhir/ValueSet/resource-types|4.0.1</t>
   </si>
   <si>
     <t>Reference.type</t>
@@ -1167,7 +1167,7 @@
     <t>Organization.address</t>
   </si>
   <si>
-    <t xml:space="preserve">Address {http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-address}
+    <t xml:space="preserve">Address {https://fhir.hl7.at/core/r4/StructureDefinition/at-core-address}
 </t>
   </si>
   <si>
@@ -1275,7 +1275,7 @@
     <t>The purpose for which you would contact a contact party.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/contactentity-type</t>
+    <t>http://hl7.org/fhir/ValueSet/contactentity-type|4.0.1</t>
   </si>
   <si>
     <t>./type</t>
@@ -1342,7 +1342,7 @@
     <t>Organization.endpoint</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Endpoint)
+    <t xml:space="preserve">Reference(Endpoint|4.0.1)
 </t>
   </si>
   <si>
@@ -1675,7 +1675,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="70.17578125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="57.515625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
